--- a/signals_2025-07.xlsx
+++ b/signals_2025-07.xlsx
@@ -4023,12 +4023,12 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>TP Oldu</t>
+          <t>SL Oldu</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>2025-08-11 17:02:44</t>
+          <t>2025-11-30 01:33:37</t>
         </is>
       </c>
     </row>
@@ -4155,12 +4155,12 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>SL Oldu</t>
+          <t>TP Oldu</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>2025-08-12 17:05:33</t>
+          <t>2025-11-30 01:33:36</t>
         </is>
       </c>
     </row>
@@ -4199,12 +4199,12 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>TP Oldu</t>
+          <t>SL Oldu</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>2025-08-13 08:05:06</t>
+          <t>2025-11-30 01:33:37</t>
         </is>
       </c>
     </row>
@@ -4287,12 +4287,12 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>TP Oldu</t>
+          <t>SL Oldu</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>2025-08-13 22:45:08</t>
+          <t>2025-11-30 01:33:35</t>
         </is>
       </c>
     </row>
@@ -4336,7 +4336,7 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>2025-08-18 03:41:16</t>
+          <t>2025-11-30 01:33:36</t>
         </is>
       </c>
     </row>
